--- a/Allas tips excel/Carls VM_Tips_2026.xlsx
+++ b/Allas tips excel/Carls VM_Tips_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CarlLing\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VM2026\Allas tips excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2AE06E-6E93-4785-B17A-A5EACF8891CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915BB6C1-99B0-4DC3-8207-895E1356133B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27000" yWindow="510" windowWidth="25455" windowHeight="15135" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instruktion" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6075" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6076" uniqueCount="933">
   <si>
     <t>Fält</t>
   </si>
@@ -2966,6 +2966,9 @@
   </si>
   <si>
     <t>Erling Haaland</t>
+  </si>
+  <si>
+    <t>Brons</t>
   </si>
 </sst>
 </file>
@@ -3791,7 +3794,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4279,10 +4282,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4311,17 +4311,17 @@
     <xf numFmtId="0" fontId="11" fillId="29" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="29" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="57" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4341,6 +4341,9 @@
     <xf numFmtId="0" fontId="16" fillId="57" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="58" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4349,6 +4352,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="58" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4369,6 +4375,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4964,23 +4971,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="201.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="201.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="189" t="s">
+    <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="200" t="s">
         <v>919</v>
       </c>
-      <c r="B1" s="190"/>
+      <c r="B1" s="201"/>
       <c r="C1" s="111"/>
       <c r="D1" s="111"/>
       <c r="E1" s="111"/>
       <c r="F1" s="111"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="182" t="s">
         <v>0</v>
       </c>
@@ -4988,7 +4995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="183" t="s">
         <v>2</v>
       </c>
@@ -4996,7 +5003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="183" t="s">
         <v>4</v>
       </c>
@@ -5004,7 +5011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="101.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="185" t="s">
         <v>6</v>
       </c>
@@ -5012,7 +5019,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="183" t="s">
         <v>7</v>
       </c>
@@ -5020,7 +5027,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="183" t="s">
         <v>8</v>
       </c>
@@ -5028,11 +5035,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="175"/>
       <c r="B9" s="175"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="183" t="s">
         <v>10</v>
       </c>
@@ -5040,11 +5047,11 @@
         <v>930</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="175"/>
       <c r="B11" s="175"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="183" t="s">
         <v>11</v>
       </c>
@@ -5062,52 +5069,55 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:AH21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AI21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="34" width="15" customWidth="1"/>
+    <col min="2" max="32" width="15" customWidth="1"/>
+    <col min="33" max="33" width="15" style="222" customWidth="1"/>
+    <col min="34" max="35" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A1" s="219" t="s">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1" s="220" t="s">
         <v>875</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="192"/>
-      <c r="Y1" s="192"/>
-      <c r="Z1" s="192"/>
-      <c r="AA1" s="192"/>
-      <c r="AB1" s="192"/>
-      <c r="AC1" s="192"/>
-      <c r="AD1" s="192"/>
-      <c r="AE1" s="192"/>
-      <c r="AF1" s="192"/>
-      <c r="AG1" s="192"/>
-      <c r="AH1" s="193"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="191"/>
+      <c r="G1" s="191"/>
+      <c r="H1" s="191"/>
+      <c r="I1" s="191"/>
+      <c r="J1" s="191"/>
+      <c r="K1" s="191"/>
+      <c r="L1" s="191"/>
+      <c r="M1" s="191"/>
+      <c r="N1" s="191"/>
+      <c r="O1" s="191"/>
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="191"/>
+      <c r="S1" s="191"/>
+      <c r="T1" s="191"/>
+      <c r="U1" s="191"/>
+      <c r="V1" s="191"/>
+      <c r="W1" s="191"/>
+      <c r="X1" s="191"/>
+      <c r="Y1" s="191"/>
+      <c r="Z1" s="191"/>
+      <c r="AA1" s="191"/>
+      <c r="AB1" s="191"/>
+      <c r="AC1" s="191"/>
+      <c r="AD1" s="191"/>
+      <c r="AE1" s="191"/>
+      <c r="AF1" s="191"/>
+      <c r="AG1" s="191"/>
+      <c r="AH1" s="191"/>
+      <c r="AI1" s="192"/>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>876</v>
       </c>
@@ -5204,14 +5214,17 @@
       <c r="AF2" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AG2" s="189" t="s">
+        <v>932</v>
+      </c>
+      <c r="AH2" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="str">
         <f>Instruktion!B10</f>
         <v>Carl Ling</v>
@@ -5341,23 +5354,27 @@
         <v>Tyskland</v>
       </c>
       <c r="AG3" s="2" t="str">
+        <f>'3. Slutspelsträd'!Q39</f>
+        <v>Belgien</v>
+      </c>
+      <c r="AH3" s="2" t="str">
         <f>'4. Skyttekung och utslagsfråga'!C4</f>
         <v>Erling Haaland</v>
       </c>
-      <c r="AH3" s="2">
+      <c r="AI3" s="2">
         <f>'4. Skyttekung och utslagsfråga'!C6</f>
         <v>314</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A6" s="220" t="s">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A6" s="221" t="s">
         <v>909</v>
       </c>
-      <c r="B6" s="192"/>
-      <c r="C6" s="192"/>
-      <c r="D6" s="193"/>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="B6" s="191"/>
+      <c r="C6" s="191"/>
+      <c r="D6" s="192"/>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -5371,7 +5388,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -5388,7 +5405,7 @@
         <v>Sydkorea</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
@@ -5405,7 +5422,7 @@
         <v>Kanada</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -5422,7 +5439,7 @@
         <v>Marocko</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
@@ -5439,7 +5456,7 @@
         <v>USA</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
@@ -5456,7 +5473,7 @@
         <v>Elfenbenskusten</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
@@ -5473,7 +5490,7 @@
         <v>Japan</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
@@ -5490,7 +5507,7 @@
         <v>Iran</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>43</v>
       </c>
@@ -5507,7 +5524,7 @@
         <v>Saudiarabien</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
@@ -5524,7 +5541,7 @@
         <v>Senegal</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -5541,7 +5558,7 @@
         <v>Algeriet</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>52</v>
       </c>
@@ -5558,7 +5575,7 @@
         <v>Uzbekistan</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>55</v>
       </c>
@@ -5575,7 +5592,7 @@
         <v>Ghana</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>910</v>
       </c>
@@ -5585,7 +5602,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="A1:AI1"/>
     <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5595,43 +5612,43 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="58" customWidth="1"/>
-    <col min="8" max="11" width="0.1796875" customWidth="1"/>
+    <col min="8" max="11" width="0.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="191" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="190" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="193"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="192"/>
       <c r="G1" s="85"/>
       <c r="H1" s="34"/>
       <c r="I1" s="34"/>
       <c r="J1" s="34"/>
     </row>
-    <row r="2" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="200" t="s">
+    <row r="2" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="199" t="s">
         <v>929</v>
       </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
+      <c r="B2" s="199"/>
+      <c r="C2" s="199"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="199"/>
       <c r="H2" s="54"/>
       <c r="I2" s="54"/>
     </row>
-    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="151" t="s">
         <v>15</v>
       </c>
@@ -5658,7 +5675,7 @@
       <c r="J3" s="82"/>
       <c r="K3" s="82"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="153" t="s">
         <v>21</v>
       </c>
@@ -5687,7 +5704,7 @@
       <c r="J4" s="84"/>
       <c r="K4" s="84"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="158" t="s">
         <v>26</v>
       </c>
@@ -5716,7 +5733,7 @@
       <c r="J5" s="84"/>
       <c r="K5" s="84"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="160" t="s">
         <v>29</v>
       </c>
@@ -5745,7 +5762,7 @@
       <c r="J6" s="84"/>
       <c r="K6" s="84"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="162" t="s">
         <v>31</v>
       </c>
@@ -5774,7 +5791,7 @@
       <c r="J7" s="84"/>
       <c r="K7" s="84"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="164" t="s">
         <v>34</v>
       </c>
@@ -5803,7 +5820,7 @@
       <c r="J8" s="84"/>
       <c r="K8" s="84"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="166" t="s">
         <v>37</v>
       </c>
@@ -5832,7 +5849,7 @@
       <c r="J9" s="84"/>
       <c r="K9" s="84"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="168" t="s">
         <v>40</v>
       </c>
@@ -5861,7 +5878,7 @@
       <c r="J10" s="84"/>
       <c r="K10" s="84"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="170" t="s">
         <v>43</v>
       </c>
@@ -5890,7 +5907,7 @@
       <c r="J11" s="84"/>
       <c r="K11" s="84"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="171" t="s">
         <v>46</v>
       </c>
@@ -5919,7 +5936,7 @@
       <c r="J12" s="84"/>
       <c r="K12" s="84"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="172" t="s">
         <v>49</v>
       </c>
@@ -5948,7 +5965,7 @@
       <c r="J13" s="84"/>
       <c r="K13" s="84"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="173" t="s">
         <v>52</v>
       </c>
@@ -5977,7 +5994,7 @@
       <c r="J14" s="84"/>
       <c r="K14" s="84"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="174" t="s">
         <v>55</v>
       </c>
@@ -6006,7 +6023,7 @@
       <c r="J15" s="84"/>
       <c r="K15" s="84"/>
     </row>
-    <row r="16" spans="1:11" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="148"/>
       <c r="B16" s="149"/>
       <c r="C16" s="148"/>
@@ -6015,7 +6032,7 @@
       <c r="F16" s="148"/>
       <c r="G16" s="112"/>
     </row>
-    <row r="17" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="87"/>
       <c r="B17" s="88"/>
       <c r="C17" s="87"/>
@@ -6024,7 +6041,7 @@
       <c r="F17" s="87"/>
       <c r="G17" s="90"/>
     </row>
-    <row r="18" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="87"/>
       <c r="B18" s="88"/>
       <c r="C18" s="87"/>
@@ -6033,7 +6050,7 @@
       <c r="F18" s="87"/>
       <c r="G18" s="90"/>
     </row>
-    <row r="19" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="87"/>
       <c r="B19" s="88"/>
       <c r="C19" s="87"/>
@@ -6042,7 +6059,7 @@
       <c r="F19" s="87"/>
       <c r="G19" s="90"/>
     </row>
-    <row r="20" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="87"/>
       <c r="B20" s="88"/>
       <c r="C20" s="87"/>
@@ -6051,7 +6068,7 @@
       <c r="F20" s="87"/>
       <c r="G20" s="90"/>
     </row>
-    <row r="21" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="87"/>
       <c r="B21" s="88"/>
       <c r="C21" s="87"/>
@@ -6060,7 +6077,7 @@
       <c r="F21" s="87"/>
       <c r="G21" s="90"/>
     </row>
-    <row r="22" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="87"/>
       <c r="B22" s="88"/>
       <c r="C22" s="87"/>
@@ -6069,7 +6086,7 @@
       <c r="F22" s="87"/>
       <c r="G22" s="90"/>
     </row>
-    <row r="23" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="87"/>
       <c r="B23" s="88"/>
       <c r="C23" s="87"/>
@@ -6078,7 +6095,7 @@
       <c r="F23" s="87"/>
       <c r="G23" s="90"/>
     </row>
-    <row r="24" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="87"/>
       <c r="B24" s="88"/>
       <c r="C24" s="87"/>
@@ -6087,7 +6104,7 @@
       <c r="F24" s="87"/>
       <c r="G24" s="90"/>
     </row>
-    <row r="25" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="87"/>
       <c r="B25" s="88"/>
       <c r="C25" s="87"/>
@@ -6096,7 +6113,7 @@
       <c r="F25" s="87"/>
       <c r="G25" s="90"/>
     </row>
-    <row r="26" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="87"/>
       <c r="B26" s="88"/>
       <c r="C26" s="87"/>
@@ -6105,7 +6122,7 @@
       <c r="F26" s="87"/>
       <c r="G26" s="90"/>
     </row>
-    <row r="27" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="87"/>
       <c r="B27" s="88"/>
       <c r="C27" s="87"/>
@@ -6114,7 +6131,7 @@
       <c r="F27" s="87"/>
       <c r="G27" s="90"/>
     </row>
-    <row r="28" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="87"/>
       <c r="B28" s="88"/>
       <c r="C28" s="87"/>
@@ -6123,7 +6140,7 @@
       <c r="F28" s="87"/>
       <c r="G28" s="90"/>
     </row>
-    <row r="29" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="87"/>
       <c r="B29" s="88"/>
       <c r="C29" s="87"/>
@@ -6132,7 +6149,7 @@
       <c r="F29" s="87"/>
       <c r="G29" s="90"/>
     </row>
-    <row r="30" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="87"/>
       <c r="B30" s="88"/>
       <c r="C30" s="87"/>
@@ -6141,7 +6158,7 @@
       <c r="F30" s="87"/>
       <c r="G30" s="90"/>
     </row>
-    <row r="31" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="87"/>
       <c r="B31" s="88"/>
       <c r="C31" s="87"/>
@@ -6150,7 +6167,7 @@
       <c r="F31" s="87"/>
       <c r="G31" s="90"/>
     </row>
-    <row r="32" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="87"/>
       <c r="B32" s="88"/>
       <c r="C32" s="87"/>
@@ -6159,7 +6176,7 @@
       <c r="F32" s="87"/>
       <c r="G32" s="90"/>
     </row>
-    <row r="33" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="87"/>
       <c r="B33" s="88"/>
       <c r="C33" s="87"/>
@@ -6168,7 +6185,7 @@
       <c r="F33" s="87"/>
       <c r="G33" s="90"/>
     </row>
-    <row r="34" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="87"/>
       <c r="B34" s="88"/>
       <c r="C34" s="87"/>
@@ -6177,7 +6194,7 @@
       <c r="F34" s="87"/>
       <c r="G34" s="90"/>
     </row>
-    <row r="35" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="87"/>
       <c r="B35" s="88"/>
       <c r="C35" s="87"/>
@@ -6186,7 +6203,7 @@
       <c r="F35" s="87"/>
       <c r="G35" s="90"/>
     </row>
-    <row r="36" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="87"/>
       <c r="B36" s="88"/>
       <c r="C36" s="87"/>
@@ -6195,7 +6212,7 @@
       <c r="F36" s="87"/>
       <c r="G36" s="90"/>
     </row>
-    <row r="37" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="87"/>
       <c r="B37" s="88"/>
       <c r="C37" s="87"/>
@@ -6204,7 +6221,7 @@
       <c r="F37" s="87"/>
       <c r="G37" s="90"/>
     </row>
-    <row r="38" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="87"/>
       <c r="B38" s="88"/>
       <c r="C38" s="87"/>
@@ -6213,7 +6230,7 @@
       <c r="F38" s="87"/>
       <c r="G38" s="90"/>
     </row>
-    <row r="39" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="87"/>
       <c r="B39" s="88"/>
       <c r="C39" s="87"/>
@@ -6222,7 +6239,7 @@
       <c r="F39" s="87"/>
       <c r="G39" s="90"/>
     </row>
-    <row r="40" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="87"/>
       <c r="B40" s="88"/>
       <c r="C40" s="87"/>
@@ -6231,7 +6248,7 @@
       <c r="F40" s="87"/>
       <c r="G40" s="90"/>
     </row>
-    <row r="41" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="87"/>
       <c r="B41" s="88"/>
       <c r="C41" s="87"/>
@@ -6240,7 +6257,7 @@
       <c r="F41" s="87"/>
       <c r="G41" s="90"/>
     </row>
-    <row r="42" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="87"/>
       <c r="B42" s="88"/>
       <c r="C42" s="87"/>
@@ -6249,7 +6266,7 @@
       <c r="F42" s="87"/>
       <c r="G42" s="90"/>
     </row>
-    <row r="43" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="87"/>
       <c r="B43" s="88"/>
       <c r="C43" s="87"/>
@@ -6258,7 +6275,7 @@
       <c r="F43" s="87"/>
       <c r="G43" s="90"/>
     </row>
-    <row r="44" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="87"/>
       <c r="B44" s="88"/>
       <c r="C44" s="87"/>
@@ -6267,7 +6284,7 @@
       <c r="F44" s="87"/>
       <c r="G44" s="90"/>
     </row>
-    <row r="45" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="87"/>
       <c r="B45" s="88"/>
       <c r="C45" s="87"/>
@@ -6276,7 +6293,7 @@
       <c r="F45" s="87"/>
       <c r="G45" s="90"/>
     </row>
-    <row r="46" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="87"/>
       <c r="B46" s="88"/>
       <c r="C46" s="87"/>
@@ -6285,7 +6302,7 @@
       <c r="F46" s="87"/>
       <c r="G46" s="90"/>
     </row>
-    <row r="47" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="87"/>
       <c r="B47" s="88"/>
       <c r="C47" s="87"/>
@@ -6294,7 +6311,7 @@
       <c r="F47" s="87"/>
       <c r="G47" s="90"/>
     </row>
-    <row r="48" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="87"/>
       <c r="B48" s="88"/>
       <c r="C48" s="87"/>
@@ -6303,7 +6320,7 @@
       <c r="F48" s="87"/>
       <c r="G48" s="90"/>
     </row>
-    <row r="49" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="87"/>
       <c r="B49" s="88"/>
       <c r="C49" s="87"/>
@@ -6312,7 +6329,7 @@
       <c r="F49" s="87"/>
       <c r="G49" s="90"/>
     </row>
-    <row r="50" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="87"/>
       <c r="B50" s="88"/>
       <c r="C50" s="87"/>
@@ -6321,7 +6338,7 @@
       <c r="F50" s="87"/>
       <c r="G50" s="90"/>
     </row>
-    <row r="51" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="87"/>
       <c r="B51" s="88"/>
       <c r="C51" s="87"/>
@@ -6330,7 +6347,7 @@
       <c r="F51" s="87"/>
       <c r="G51" s="90"/>
     </row>
-    <row r="52" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="90"/>
       <c r="B52" s="90"/>
       <c r="C52" s="90"/>
@@ -6339,7 +6356,7 @@
       <c r="F52" s="90"/>
       <c r="G52" s="90"/>
     </row>
-    <row r="53" spans="1:7" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="90"/>
       <c r="C53" s="90"/>
@@ -6348,7 +6365,7 @@
       <c r="F53" s="90"/>
       <c r="G53" s="90"/>
     </row>
-    <row r="54" spans="1:7" s="111" customFormat="1" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" s="111" customFormat="1" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="112"/>
       <c r="B54" s="112"/>
       <c r="C54" s="112"/>
@@ -6357,7 +6374,7 @@
       <c r="F54" s="112"/>
       <c r="G54" s="112"/>
     </row>
-    <row r="55" spans="1:7" s="111" customFormat="1" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" s="111" customFormat="1" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="112"/>
       <c r="B55" s="112"/>
       <c r="C55" s="112"/>
@@ -6366,7 +6383,7 @@
       <c r="F55" s="112"/>
       <c r="G55" s="112"/>
     </row>
-    <row r="56" spans="1:7" s="111" customFormat="1" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" s="111" customFormat="1" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="112"/>
       <c r="B56" s="112"/>
       <c r="C56" s="112"/>
@@ -6375,7 +6392,7 @@
       <c r="F56" s="112"/>
       <c r="G56" s="112"/>
     </row>
-    <row r="57" spans="1:7" s="111" customFormat="1" ht="0.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" s="111" customFormat="1" ht="0.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="112"/>
       <c r="B57" s="112"/>
       <c r="C57" s="112"/>
@@ -6384,7 +6401,7 @@
       <c r="F57" s="112"/>
       <c r="G57" s="112"/>
     </row>
-    <row r="58" spans="1:7" s="111" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" s="111" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="112"/>
       <c r="B58" s="112"/>
       <c r="C58" s="112"/>
@@ -6396,23 +6413,23 @@
       </c>
       <c r="G58" s="112"/>
     </row>
-    <row r="59" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="197" t="s">
+    <row r="59" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="196" t="s">
         <v>922</v>
       </c>
-      <c r="C59" s="198"/>
-      <c r="D59" s="198"/>
-      <c r="E59" s="199"/>
-    </row>
-    <row r="60" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="194" t="s">
+      <c r="C59" s="197"/>
+      <c r="D59" s="197"/>
+      <c r="E59" s="198"/>
+    </row>
+    <row r="60" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="193" t="s">
         <v>312</v>
       </c>
-      <c r="B60" s="195"/>
-      <c r="C60" s="195"/>
-      <c r="D60" s="196"/>
-    </row>
-    <row r="61" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="194"/>
+      <c r="C60" s="194"/>
+      <c r="D60" s="195"/>
+    </row>
+    <row r="61" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="91" t="s">
         <v>15</v>
       </c>
@@ -6426,7 +6443,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="93" t="s">
         <v>21</v>
       </c>
@@ -6444,7 +6461,7 @@
       </c>
       <c r="G62" s="121"/>
     </row>
-    <row r="63" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="95" t="s">
         <v>26</v>
       </c>
@@ -6461,7 +6478,7 @@
         <v>Kanada</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="97" t="s">
         <v>29</v>
       </c>
@@ -6478,7 +6495,7 @@
         <v>Marocko</v>
       </c>
     </row>
-    <row r="65" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="99" t="s">
         <v>31</v>
       </c>
@@ -6495,7 +6512,7 @@
         <v>USA</v>
       </c>
     </row>
-    <row r="66" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="101" t="s">
         <v>34</v>
       </c>
@@ -6512,7 +6529,7 @@
         <v>Elfenbenskusten</v>
       </c>
     </row>
-    <row r="67" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="103" t="s">
         <v>37</v>
       </c>
@@ -6529,7 +6546,7 @@
         <v>Japan</v>
       </c>
     </row>
-    <row r="68" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="105" t="s">
         <v>40</v>
       </c>
@@ -6546,7 +6563,7 @@
         <v>Iran</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="106" t="s">
         <v>43</v>
       </c>
@@ -6563,7 +6580,7 @@
         <v>Saudiarabien</v>
       </c>
     </row>
-    <row r="70" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="107" t="s">
         <v>46</v>
       </c>
@@ -6580,7 +6597,7 @@
         <v>Senegal</v>
       </c>
     </row>
-    <row r="71" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="108" t="s">
         <v>49</v>
       </c>
@@ -6597,7 +6614,7 @@
         <v>Algeriet</v>
       </c>
     </row>
-    <row r="72" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="109" t="s">
         <v>52</v>
       </c>
@@ -6614,7 +6631,7 @@
         <v>Uzbekistan</v>
       </c>
     </row>
-    <row r="73" spans="1:6" s="111" customFormat="1" ht="3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" s="111" customFormat="1" ht="3" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="110" t="s">
         <v>55</v>
       </c>
@@ -6631,49 +6648,49 @@
         <v>Ghana</v>
       </c>
     </row>
-    <row r="74" spans="1:6" s="111" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:6" s="111" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:6" s="111" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:6" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:6" s="111" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:6" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" s="111" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:6" s="111" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:6" s="111" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:6" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:6" s="111" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:6" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F79"/>
     </row>
-    <row r="80" spans="1:6" s="111" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" spans="6:7" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" s="111" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="6:7" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F81"/>
     </row>
-    <row r="82" spans="6:7" s="111" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="6:7" s="111" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F82"/>
     </row>
-    <row r="83" spans="6:7" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="6:7" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F83"/>
     </row>
-    <row r="84" spans="6:7" s="111" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="6:7" s="111" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F84"/>
       <c r="G84"/>
     </row>
-    <row r="85" spans="6:7" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="6:7" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F85"/>
       <c r="G85"/>
     </row>
-    <row r="86" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" spans="6:7" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="6:7" s="111" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F87"/>
       <c r="G87"/>
     </row>
-    <row r="88" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" spans="6:7" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" spans="6:7" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="6:7" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="6:7" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F94" s="4"/>
     </row>
-    <row r="95" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="96" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="6:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -6846,36 +6863,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" customWidth="1"/>
-    <col min="6" max="6" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="191" t="s">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="190" t="s">
         <v>918</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="193"/>
-    </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="201" t="s">
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="192"/>
+    </row>
+    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="202" t="s">
         <v>923</v>
       </c>
-      <c r="B2" s="201"/>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
-    </row>
-    <row r="3" spans="1:6" ht="5.15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="202"/>
+      <c r="C2" s="202"/>
+      <c r="D2" s="202"/>
+      <c r="E2" s="202"/>
+      <c r="F2" s="202"/>
+    </row>
+    <row r="3" spans="1:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="116" t="s">
         <v>920</v>
       </c>
@@ -6883,11 +6900,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="111"/>
       <c r="B5" s="116"/>
     </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="116" t="s">
         <v>920</v>
       </c>
@@ -6895,11 +6912,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="111"/>
       <c r="B7" s="116"/>
     </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="116" t="s">
         <v>920</v>
       </c>
@@ -6907,11 +6924,11 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="111"/>
       <c r="B9" s="116"/>
     </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="116" t="s">
         <v>920</v>
       </c>
@@ -6919,11 +6936,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="111"/>
       <c r="B11" s="116"/>
     </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="116" t="s">
         <v>920</v>
       </c>
@@ -6931,14 +6948,14 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="111"/>
       <c r="B13" s="117"/>
       <c r="C13" s="111"/>
       <c r="D13" s="111"/>
       <c r="E13" s="111"/>
     </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="116" t="s">
         <v>920</v>
       </c>
@@ -6946,10 +6963,10 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="116"/>
     </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="116" t="s">
         <v>920</v>
       </c>
@@ -6957,10 +6974,10 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="116"/>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="116" t="s">
         <v>920</v>
       </c>
@@ -6968,18 +6985,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="197" t="s">
+    <row r="19" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="196" t="s">
         <v>922</v>
       </c>
-      <c r="C20" s="198"/>
-      <c r="D20" s="199"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="C20" s="197"/>
+      <c r="D20" s="198"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G27" s="177"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F30" s="111"/>
       <c r="G30" s="177"/>
       <c r="H30" s="177"/>
@@ -6988,12 +7005,12 @@
       <c r="K30" s="177"/>
       <c r="L30" s="111"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E32" s="111"/>
       <c r="F32" s="111"/>
       <c r="G32" s="111"/>
     </row>
-    <row r="33" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E33" s="111"/>
       <c r="F33" s="177"/>
       <c r="G33" s="111"/>
@@ -7070,44 +7087,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:AI53"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.7265625" style="113" customWidth="1"/>
-    <col min="2" max="2" width="6.7265625" style="113" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" style="113" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" style="113" customWidth="1"/>
-    <col min="5" max="5" width="5.7265625" style="113" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="113"/>
-    <col min="7" max="7" width="15.7265625" style="113" customWidth="1"/>
-    <col min="8" max="8" width="5.7265625" style="113" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" style="113" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" style="113" customWidth="1"/>
-    <col min="11" max="11" width="5.7265625" style="113" customWidth="1"/>
-    <col min="12" max="12" width="9.1796875" style="113"/>
-    <col min="13" max="13" width="15.7265625" style="113" customWidth="1"/>
-    <col min="14" max="14" width="9.1796875" style="113"/>
-    <col min="15" max="15" width="5.7265625" style="113" customWidth="1"/>
-    <col min="16" max="18" width="15.7265625" style="113" customWidth="1"/>
-    <col min="19" max="19" width="5.7265625" style="113" customWidth="1"/>
-    <col min="20" max="20" width="9.1796875" style="113"/>
-    <col min="21" max="21" width="15.7265625" style="113" customWidth="1"/>
-    <col min="22" max="22" width="9.1796875" style="113"/>
-    <col min="23" max="23" width="5.7265625" style="113" customWidth="1"/>
-    <col min="24" max="24" width="15.7265625" style="113" customWidth="1"/>
-    <col min="25" max="25" width="5.7265625" style="113" customWidth="1"/>
-    <col min="26" max="26" width="9.1796875" style="113"/>
-    <col min="27" max="27" width="15.7265625" style="113" customWidth="1"/>
-    <col min="28" max="28" width="9.1796875" style="113"/>
-    <col min="29" max="29" width="5.7265625" style="113" customWidth="1"/>
-    <col min="30" max="30" width="15.7265625" style="113" customWidth="1"/>
-    <col min="31" max="31" width="12.54296875" style="113" customWidth="1"/>
-    <col min="32" max="32" width="8.1796875" style="113" customWidth="1"/>
-    <col min="33" max="33" width="10.26953125" style="113" customWidth="1"/>
-    <col min="34" max="16384" width="9.1796875" style="113"/>
+    <col min="1" max="1" width="1.7109375" style="113" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" style="113" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="113" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="113" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" style="113" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="113"/>
+    <col min="7" max="7" width="15.7109375" style="113" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" style="113" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" style="113" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="113" customWidth="1"/>
+    <col min="11" max="11" width="5.7109375" style="113" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="113"/>
+    <col min="13" max="13" width="15.7109375" style="113" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="113"/>
+    <col min="15" max="15" width="5.7109375" style="113" customWidth="1"/>
+    <col min="16" max="18" width="15.7109375" style="113" customWidth="1"/>
+    <col min="19" max="19" width="5.7109375" style="113" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" style="113"/>
+    <col min="21" max="21" width="15.7109375" style="113" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" style="113"/>
+    <col min="23" max="23" width="5.7109375" style="113" customWidth="1"/>
+    <col min="24" max="24" width="15.7109375" style="113" customWidth="1"/>
+    <col min="25" max="25" width="5.7109375" style="113" customWidth="1"/>
+    <col min="26" max="26" width="9.140625" style="113"/>
+    <col min="27" max="27" width="15.7109375" style="113" customWidth="1"/>
+    <col min="28" max="28" width="9.140625" style="113"/>
+    <col min="29" max="29" width="5.7109375" style="113" customWidth="1"/>
+    <col min="30" max="30" width="15.7109375" style="113" customWidth="1"/>
+    <col min="31" max="31" width="12.5703125" style="113" customWidth="1"/>
+    <col min="32" max="32" width="8.140625" style="113" customWidth="1"/>
+    <col min="33" max="33" width="10.28515625" style="113" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="113"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:35" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:35" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B2" s="124"/>
       <c r="C2" s="125"/>
       <c r="D2" s="125"/>
@@ -7140,37 +7157,37 @@
       <c r="AE2" s="125"/>
       <c r="AF2" s="126"/>
     </row>
-    <row r="3" spans="2:35" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:35" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="127"/>
-      <c r="O3" s="205" t="s">
+      <c r="O3" s="204" t="s">
         <v>353</v>
       </c>
-      <c r="P3" s="206"/>
-      <c r="Q3" s="206"/>
-      <c r="R3" s="206"/>
-      <c r="S3" s="207"/>
+      <c r="P3" s="205"/>
+      <c r="Q3" s="205"/>
+      <c r="R3" s="205"/>
+      <c r="S3" s="206"/>
       <c r="AF3" s="128"/>
     </row>
-    <row r="4" spans="2:35" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="127"/>
-      <c r="C4" s="202" t="s">
+      <c r="C4" s="210" t="s">
         <v>914</v>
       </c>
-      <c r="D4" s="202"/>
-      <c r="E4" s="202"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="209"/>
-      <c r="Q4" s="209"/>
-      <c r="R4" s="209"/>
-      <c r="S4" s="210"/>
-      <c r="AC4" s="202" t="s">
+      <c r="D4" s="210"/>
+      <c r="E4" s="210"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="208"/>
+      <c r="R4" s="208"/>
+      <c r="S4" s="209"/>
+      <c r="AC4" s="210" t="s">
         <v>914</v>
       </c>
-      <c r="AD4" s="202"/>
-      <c r="AE4" s="202"/>
+      <c r="AD4" s="210"/>
+      <c r="AE4" s="210"/>
       <c r="AF4" s="128"/>
     </row>
-    <row r="5" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="129"/>
       <c r="C5" s="114"/>
       <c r="D5" s="114"/>
@@ -7206,9 +7223,9 @@
       <c r="AH5" s="114"/>
       <c r="AI5" s="114"/>
     </row>
-    <row r="6" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="127"/>
-      <c r="C6" s="204" t="s">
+      <c r="C6" s="214" t="s">
         <v>251</v>
       </c>
       <c r="D6" s="115" t="str">
@@ -7250,15 +7267,15 @@
       <c r="AH6" s="114"/>
       <c r="AI6" s="114"/>
     </row>
-    <row r="7" spans="2:35" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="127"/>
-      <c r="C7" s="204"/>
+      <c r="C7" s="214"/>
       <c r="E7" s="114"/>
-      <c r="F7" s="202" t="s">
+      <c r="F7" s="210" t="s">
         <v>913</v>
       </c>
-      <c r="G7" s="202"/>
-      <c r="H7" s="202"/>
+      <c r="G7" s="210"/>
+      <c r="H7" s="210"/>
       <c r="I7" s="114"/>
       <c r="J7" s="114"/>
       <c r="K7" s="114"/>
@@ -7276,11 +7293,11 @@
       <c r="W7" s="114"/>
       <c r="X7" s="114"/>
       <c r="Y7" s="114"/>
-      <c r="Z7" s="202" t="s">
+      <c r="Z7" s="210" t="s">
         <v>913</v>
       </c>
-      <c r="AA7" s="202"/>
-      <c r="AB7" s="202"/>
+      <c r="AA7" s="210"/>
+      <c r="AB7" s="210"/>
       <c r="AC7" s="114"/>
       <c r="AE7" s="203"/>
       <c r="AF7" s="128"/>
@@ -7288,9 +7305,9 @@
       <c r="AH7" s="114"/>
       <c r="AI7" s="114"/>
     </row>
-    <row r="8" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="127"/>
-      <c r="C8" s="204"/>
+      <c r="C8" s="214"/>
       <c r="D8" s="122" t="str">
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M74",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>USA</v>
@@ -7330,7 +7347,7 @@
       <c r="AH8" s="114"/>
       <c r="AI8" s="114"/>
     </row>
-    <row r="9" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="131"/>
       <c r="C9" s="123"/>
       <c r="D9" s="114"/>
@@ -7367,7 +7384,7 @@
       <c r="AH9" s="114"/>
       <c r="AI9" s="114"/>
     </row>
-    <row r="10" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="131"/>
       <c r="C10" s="123"/>
       <c r="D10" s="114"/>
@@ -7399,7 +7416,7 @@
       <c r="AH10" s="114"/>
       <c r="AI10" s="114"/>
     </row>
-    <row r="11" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="131"/>
       <c r="C11" s="123"/>
       <c r="D11" s="114"/>
@@ -7438,7 +7455,7 @@
       <c r="AH11" s="114"/>
       <c r="AI11" s="114"/>
     </row>
-    <row r="12" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="127"/>
       <c r="C12" s="203" t="s">
         <v>252</v>
@@ -7477,7 +7494,7 @@
       <c r="AH12" s="114"/>
       <c r="AI12" s="114"/>
     </row>
-    <row r="13" spans="2:35" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="127"/>
       <c r="C13" s="203"/>
       <c r="D13" s="114"/>
@@ -7485,22 +7502,22 @@
       <c r="F13" s="114"/>
       <c r="G13" s="114"/>
       <c r="H13" s="114"/>
-      <c r="I13" s="202" t="s">
+      <c r="I13" s="210" t="s">
         <v>915</v>
       </c>
-      <c r="J13" s="202"/>
-      <c r="K13" s="202"/>
+      <c r="J13" s="210"/>
+      <c r="K13" s="210"/>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
       <c r="N13" s="114"/>
       <c r="T13" s="114"/>
       <c r="U13" s="114"/>
       <c r="V13" s="114"/>
-      <c r="W13" s="202" t="s">
+      <c r="W13" s="210" t="s">
         <v>915</v>
       </c>
-      <c r="X13" s="202"/>
-      <c r="Y13" s="202"/>
+      <c r="X13" s="210"/>
+      <c r="Y13" s="210"/>
       <c r="Z13" s="114"/>
       <c r="AA13" s="114"/>
       <c r="AB13" s="114"/>
@@ -7511,7 +7528,7 @@
       <c r="AH13" s="114"/>
       <c r="AI13" s="114"/>
     </row>
-    <row r="14" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="127"/>
       <c r="C14" s="203"/>
       <c r="D14" s="122" t="str">
@@ -7550,7 +7567,7 @@
       <c r="AH14" s="114"/>
       <c r="AI14" s="114"/>
     </row>
-    <row r="15" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="129"/>
       <c r="C15" s="114"/>
       <c r="D15" s="114"/>
@@ -7590,7 +7607,7 @@
       <c r="AH15" s="114"/>
       <c r="AI15" s="114"/>
     </row>
-    <row r="16" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="129"/>
       <c r="C16" s="114"/>
       <c r="D16" s="114"/>
@@ -7624,7 +7641,7 @@
       <c r="AH16" s="114"/>
       <c r="AI16" s="114"/>
     </row>
-    <row r="17" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="129"/>
       <c r="C17" s="114"/>
       <c r="D17" s="114"/>
@@ -7662,7 +7679,7 @@
       <c r="AH17" s="114"/>
       <c r="AI17" s="114"/>
     </row>
-    <row r="18" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="127"/>
       <c r="C18" s="203" t="s">
         <v>249</v>
@@ -7710,7 +7727,7 @@
       <c r="AH18" s="114"/>
       <c r="AI18" s="114"/>
     </row>
-    <row r="19" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="127"/>
       <c r="C19" s="203"/>
       <c r="D19" s="114"/>
@@ -7747,7 +7764,7 @@
       <c r="AH19" s="114"/>
       <c r="AI19" s="114"/>
     </row>
-    <row r="20" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="127"/>
       <c r="C20" s="203"/>
       <c r="D20" s="115" t="str">
@@ -7787,7 +7804,7 @@
       <c r="AH20" s="114"/>
       <c r="AI20" s="114"/>
     </row>
-    <row r="21" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="127"/>
       <c r="E21" s="114"/>
       <c r="F21" s="203" t="s">
@@ -7831,7 +7848,7 @@
       <c r="AH21" s="114"/>
       <c r="AI21" s="114"/>
     </row>
-    <row r="22" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="127"/>
       <c r="E22" s="114"/>
       <c r="F22" s="203"/>
@@ -7864,7 +7881,7 @@
       <c r="AH22" s="114"/>
       <c r="AI22" s="114"/>
     </row>
-    <row r="23" spans="2:35" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:35" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="127"/>
       <c r="E23" s="114"/>
       <c r="F23" s="203"/>
@@ -7879,11 +7896,11 @@
       <c r="M23" s="114"/>
       <c r="N23" s="114"/>
       <c r="O23" s="114"/>
-      <c r="P23" s="202" t="s">
+      <c r="P23" s="210" t="s">
         <v>318</v>
       </c>
-      <c r="Q23" s="202"/>
-      <c r="R23" s="202"/>
+      <c r="Q23" s="210"/>
+      <c r="R23" s="210"/>
       <c r="S23" s="114"/>
       <c r="T23" s="114"/>
       <c r="U23" s="114"/>
@@ -7902,7 +7919,7 @@
       <c r="AH23" s="114"/>
       <c r="AI23" s="114"/>
     </row>
-    <row r="24" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="127"/>
       <c r="C24" s="203" t="s">
         <v>250</v>
@@ -7945,7 +7962,7 @@
       <c r="AH24" s="114"/>
       <c r="AI24" s="114"/>
     </row>
-    <row r="25" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="127"/>
       <c r="C25" s="203"/>
       <c r="D25" s="114"/>
@@ -7978,7 +7995,7 @@
       <c r="AH25" s="114"/>
       <c r="AI25" s="114"/>
     </row>
-    <row r="26" spans="2:35" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="127"/>
       <c r="C26" s="203"/>
       <c r="D26" s="115" t="str">
@@ -7992,11 +8009,11 @@
       <c r="I26" s="114"/>
       <c r="J26" s="114"/>
       <c r="K26" s="114"/>
-      <c r="L26" s="202" t="s">
+      <c r="L26" s="210" t="s">
         <v>916</v>
       </c>
-      <c r="M26" s="202"/>
-      <c r="N26" s="202"/>
+      <c r="M26" s="210"/>
+      <c r="N26" s="210"/>
       <c r="O26" s="114"/>
       <c r="P26" s="211" t="s">
         <v>922</v>
@@ -8004,11 +8021,11 @@
       <c r="Q26" s="212"/>
       <c r="R26" s="213"/>
       <c r="S26" s="114"/>
-      <c r="T26" s="202" t="s">
+      <c r="T26" s="210" t="s">
         <v>916</v>
       </c>
-      <c r="U26" s="202"/>
-      <c r="V26" s="202"/>
+      <c r="U26" s="210"/>
+      <c r="V26" s="210"/>
       <c r="W26" s="114"/>
       <c r="Z26" s="114"/>
       <c r="AA26" s="114"/>
@@ -8024,7 +8041,7 @@
       <c r="AH26" s="114"/>
       <c r="AI26" s="114"/>
     </row>
-    <row r="27" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="127"/>
       <c r="E27" s="114"/>
       <c r="F27" s="114"/>
@@ -8058,7 +8075,7 @@
       <c r="AH27" s="114"/>
       <c r="AI27" s="114"/>
     </row>
-    <row r="28" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="127"/>
       <c r="E28" s="114"/>
       <c r="F28" s="114"/>
@@ -8099,7 +8116,7 @@
       <c r="AH28" s="114"/>
       <c r="AI28" s="114"/>
     </row>
-    <row r="29" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="127"/>
       <c r="E29" s="114"/>
       <c r="F29" s="114"/>
@@ -8130,7 +8147,7 @@
       <c r="AH29" s="114"/>
       <c r="AI29" s="114"/>
     </row>
-    <row r="30" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="127"/>
       <c r="E30" s="114"/>
       <c r="F30" s="114"/>
@@ -8167,7 +8184,7 @@
       <c r="AH30" s="114"/>
       <c r="AI30" s="114"/>
     </row>
-    <row r="31" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="129"/>
       <c r="C31" s="114"/>
       <c r="D31" s="114"/>
@@ -8203,7 +8220,7 @@
       <c r="AH31" s="114"/>
       <c r="AI31" s="114"/>
     </row>
-    <row r="32" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="127"/>
       <c r="C32" s="203" t="s">
         <v>257</v>
@@ -8246,7 +8263,7 @@
       <c r="AH32" s="114"/>
       <c r="AI32" s="114"/>
     </row>
-    <row r="33" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="127"/>
       <c r="C33" s="203"/>
       <c r="D33" s="114"/>
@@ -8278,7 +8295,7 @@
       <c r="AH33" s="114"/>
       <c r="AI33" s="114"/>
     </row>
-    <row r="34" spans="2:35" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="127"/>
       <c r="C34" s="203"/>
       <c r="D34" s="115" t="str">
@@ -8295,11 +8312,11 @@
       <c r="M34" s="114"/>
       <c r="N34" s="114"/>
       <c r="O34" s="114"/>
-      <c r="P34" s="202" t="s">
+      <c r="P34" s="210" t="s">
         <v>917</v>
       </c>
-      <c r="Q34" s="202"/>
-      <c r="R34" s="202"/>
+      <c r="Q34" s="210"/>
+      <c r="R34" s="210"/>
       <c r="S34" s="114"/>
       <c r="T34" s="114"/>
       <c r="U34" s="114"/>
@@ -8321,7 +8338,7 @@
       <c r="AH34" s="114"/>
       <c r="AI34" s="114"/>
     </row>
-    <row r="35" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="129"/>
       <c r="C35" s="114"/>
       <c r="D35" s="114"/>
@@ -8364,7 +8381,7 @@
       <c r="AH35" s="114"/>
       <c r="AI35" s="114"/>
     </row>
-    <row r="36" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="129"/>
       <c r="C36" s="114"/>
       <c r="D36" s="114"/>
@@ -8402,7 +8419,7 @@
       <c r="AH36" s="114"/>
       <c r="AI36" s="114"/>
     </row>
-    <row r="37" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="127"/>
       <c r="E37" s="114"/>
       <c r="F37" s="203"/>
@@ -8423,7 +8440,7 @@
       <c r="AH37" s="114"/>
       <c r="AI37" s="114"/>
     </row>
-    <row r="38" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="127"/>
       <c r="C38" s="203" t="s">
         <v>258</v>
@@ -8471,7 +8488,7 @@
       <c r="AH38" s="114"/>
       <c r="AI38" s="114"/>
     </row>
-    <row r="39" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="127"/>
       <c r="C39" s="203"/>
       <c r="D39" s="114"/>
@@ -8505,7 +8522,7 @@
       <c r="AH39" s="114"/>
       <c r="AI39" s="114"/>
     </row>
-    <row r="40" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="127"/>
       <c r="C40" s="203"/>
       <c r="D40" s="115" t="str">
@@ -8541,7 +8558,7 @@
       <c r="AH40" s="114"/>
       <c r="AI40" s="114"/>
     </row>
-    <row r="41" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="129"/>
       <c r="C41" s="114"/>
       <c r="D41" s="114"/>
@@ -8581,7 +8598,7 @@
       <c r="AH41" s="114"/>
       <c r="AI41" s="114"/>
     </row>
-    <row r="42" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="129"/>
       <c r="C42" s="114"/>
       <c r="D42" s="114"/>
@@ -8616,7 +8633,7 @@
       <c r="AH42" s="114"/>
       <c r="AI42" s="114"/>
     </row>
-    <row r="43" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="127"/>
       <c r="D43" s="114"/>
       <c r="E43" s="114"/>
@@ -8653,7 +8670,7 @@
       <c r="AH43" s="114"/>
       <c r="AI43" s="114"/>
     </row>
-    <row r="44" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="127"/>
       <c r="C44" s="203" t="s">
         <v>259</v>
@@ -8699,7 +8716,7 @@
       <c r="AH44" s="114"/>
       <c r="AI44" s="114"/>
     </row>
-    <row r="45" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="127"/>
       <c r="C45" s="203"/>
       <c r="D45" s="114"/>
@@ -8733,7 +8750,7 @@
       <c r="AH45" s="114"/>
       <c r="AI45" s="114"/>
     </row>
-    <row r="46" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="127"/>
       <c r="C46" s="203"/>
       <c r="D46" s="122" t="str">
@@ -8775,7 +8792,7 @@
       <c r="AH46" s="114"/>
       <c r="AI46" s="114"/>
     </row>
-    <row r="47" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="127"/>
       <c r="D47" s="114"/>
       <c r="E47" s="114"/>
@@ -8815,7 +8832,7 @@
       <c r="AH47" s="114"/>
       <c r="AI47" s="114"/>
     </row>
-    <row r="48" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="127"/>
       <c r="D48" s="114"/>
       <c r="E48" s="114"/>
@@ -8848,7 +8865,7 @@
       <c r="AH48" s="114"/>
       <c r="AI48" s="114"/>
     </row>
-    <row r="49" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="129"/>
       <c r="C49" s="114"/>
       <c r="D49" s="114"/>
@@ -8886,7 +8903,7 @@
       <c r="AH49" s="114"/>
       <c r="AI49" s="114"/>
     </row>
-    <row r="50" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="127"/>
       <c r="C50" s="203" t="s">
         <v>260</v>
@@ -8932,7 +8949,7 @@
       <c r="AH50" s="114"/>
       <c r="AI50" s="114"/>
     </row>
-    <row r="51" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="127"/>
       <c r="C51" s="203"/>
       <c r="D51" s="114"/>
@@ -8967,7 +8984,7 @@
       <c r="AH51" s="114"/>
       <c r="AI51" s="114"/>
     </row>
-    <row r="52" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="127"/>
       <c r="C52" s="203"/>
       <c r="D52" s="122" t="str">
@@ -9009,7 +9026,7 @@
       <c r="AH52" s="114"/>
       <c r="AI52" s="114"/>
     </row>
-    <row r="53" spans="2:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="133"/>
       <c r="C53" s="134"/>
       <c r="D53" s="134"/>
@@ -9047,6 +9064,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="AE50:AE52"/>
+    <mergeCell ref="AE44:AE46"/>
+    <mergeCell ref="AE38:AE40"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AB21:AB23"/>
+    <mergeCell ref="AE18:AE20"/>
+    <mergeCell ref="AE12:AE14"/>
+    <mergeCell ref="Z7:AB7"/>
+    <mergeCell ref="AB35:AB37"/>
+    <mergeCell ref="AB47:AB49"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C24:C26"/>
     <mergeCell ref="F47:F49"/>
     <mergeCell ref="AE32:AE34"/>
     <mergeCell ref="AE24:AE26"/>
@@ -9059,36 +9102,10 @@
     <mergeCell ref="P26:R26"/>
     <mergeCell ref="P34:R34"/>
     <mergeCell ref="T26:V26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C24:C26"/>
     <mergeCell ref="L28:L30"/>
     <mergeCell ref="I41:I43"/>
     <mergeCell ref="I15:I17"/>
     <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="AE50:AE52"/>
-    <mergeCell ref="AE44:AE46"/>
-    <mergeCell ref="AE38:AE40"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AB21:AB23"/>
-    <mergeCell ref="AE18:AE20"/>
-    <mergeCell ref="AE12:AE14"/>
-    <mergeCell ref="Z7:AB7"/>
-    <mergeCell ref="AB35:AB37"/>
-    <mergeCell ref="AB47:AB49"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="C18:C20"/>
   </mergeCells>
   <conditionalFormatting sqref="P26:R26">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -9207,33 +9224,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D55ECB75-4A40-4E5A-88E0-6C857442FEED}">
   <dimension ref="A1:AX18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="20.453125" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
     <col min="4" max="50" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="111" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="191" t="s">
+    <row r="1" spans="1:50" s="111" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="190" t="s">
         <v>925</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="193"/>
-    </row>
-    <row r="2" spans="1:50" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="201" t="s">
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="192"/>
+    </row>
+    <row r="2" spans="1:50" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="202" t="s">
         <v>924</v>
       </c>
-      <c r="B2" s="201"/>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="B2" s="202"/>
+      <c r="C2" s="202"/>
+      <c r="D2" s="202"/>
+      <c r="E2" s="202"/>
+      <c r="F2" s="202"/>
       <c r="K2" s="111"/>
       <c r="L2" s="111"/>
       <c r="M2" s="111"/>
@@ -9275,7 +9292,7 @@
       <c r="AW2" s="111"/>
       <c r="AX2" s="111"/>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="K3" s="111"/>
       <c r="L3" s="111"/>
       <c r="M3" s="111"/>
@@ -9317,7 +9334,7 @@
       <c r="AW3" s="111"/>
       <c r="AX3" s="111"/>
     </row>
-    <row r="4" spans="1:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="179" t="s">
         <v>926</v>
       </c>
@@ -9365,7 +9382,7 @@
       <c r="AW4" s="111"/>
       <c r="AX4" s="111"/>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="B5" s="180"/>
       <c r="K5" s="111"/>
       <c r="L5" s="111"/>
@@ -9408,7 +9425,7 @@
       <c r="AW5" s="111"/>
       <c r="AX5" s="111"/>
     </row>
-    <row r="6" spans="1:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="179" t="s">
         <v>927</v>
       </c>
@@ -9456,7 +9473,7 @@
       <c r="AW6" s="111"/>
       <c r="AX6" s="111"/>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="K7" s="111"/>
       <c r="L7" s="111"/>
       <c r="M7" s="111"/>
@@ -9498,7 +9515,7 @@
       <c r="AW7" s="111"/>
       <c r="AX7" s="111"/>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
       <c r="K8" s="111"/>
       <c r="L8" s="111"/>
       <c r="M8" s="111"/>
@@ -9540,7 +9557,7 @@
       <c r="AW8" s="111"/>
       <c r="AX8" s="111"/>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
       <c r="K9" s="111"/>
       <c r="L9" s="111"/>
       <c r="M9" s="111"/>
@@ -9582,7 +9599,7 @@
       <c r="AW9" s="111"/>
       <c r="AX9" s="111"/>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
       <c r="K10" s="111"/>
       <c r="L10" s="111"/>
       <c r="M10" s="111"/>
@@ -9624,7 +9641,7 @@
       <c r="AW10" s="111"/>
       <c r="AX10" s="111"/>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
       <c r="K11" s="111"/>
       <c r="L11" s="111"/>
       <c r="M11" s="111"/>
@@ -9666,7 +9683,7 @@
       <c r="AW11" s="111"/>
       <c r="AX11" s="111"/>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
       <c r="E12" s="111"/>
       <c r="F12" s="111"/>
       <c r="G12" s="111"/>
@@ -9714,7 +9731,7 @@
       <c r="AW12" s="111"/>
       <c r="AX12" s="111"/>
     </row>
-    <row r="13" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" s="178"/>
       <c r="F13" s="111"/>
       <c r="G13" s="111"/>
@@ -9722,7 +9739,7 @@
       <c r="I13" s="111"/>
       <c r="J13" s="111"/>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
       <c r="E14" s="177"/>
       <c r="F14" s="177"/>
       <c r="G14" s="177"/>
@@ -9730,7 +9747,7 @@
       <c r="I14" s="177"/>
       <c r="J14" s="177"/>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
       <c r="E15" s="111"/>
       <c r="F15" s="111"/>
       <c r="G15" s="111"/>
@@ -9738,7 +9755,7 @@
       <c r="I15" s="111"/>
       <c r="J15" s="111"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F18" s="116"/>
     </row>
   </sheetData>
@@ -9753,7 +9770,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H50"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -9762,20 +9779,20 @@
     <col min="6" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="214" t="s">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="215" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="193"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="192"/>
       <c r="F1" s="34" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="34"/>
       <c r="H1" s="34"/>
     </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
@@ -9798,7 +9815,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -9817,7 +9834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>21</v>
       </c>
@@ -9836,7 +9853,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>21</v>
       </c>
@@ -9855,7 +9872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
@@ -9874,7 +9891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>26</v>
       </c>
@@ -9893,7 +9910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>26</v>
       </c>
@@ -9912,7 +9929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>26</v>
       </c>
@@ -9931,7 +9948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>26</v>
       </c>
@@ -9950,7 +9967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>29</v>
       </c>
@@ -9969,7 +9986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>29</v>
       </c>
@@ -9988,7 +10005,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>29</v>
       </c>
@@ -10007,7 +10024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>29</v>
       </c>
@@ -10026,7 +10043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>31</v>
       </c>
@@ -10038,7 +10055,7 @@
       </c>
       <c r="D15" s="17"/>
     </row>
-    <row r="16" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>31</v>
       </c>
@@ -10050,7 +10067,7 @@
       </c>
       <c r="D16" s="17"/>
     </row>
-    <row r="17" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>31</v>
       </c>
@@ -10062,7 +10079,7 @@
       </c>
       <c r="D17" s="17"/>
     </row>
-    <row r="18" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>31</v>
       </c>
@@ -10074,7 +10091,7 @@
       </c>
       <c r="D18" s="17"/>
     </row>
-    <row r="19" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
         <v>34</v>
       </c>
@@ -10086,7 +10103,7 @@
       </c>
       <c r="D19" s="20"/>
     </row>
-    <row r="20" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
         <v>34</v>
       </c>
@@ -10098,7 +10115,7 @@
       </c>
       <c r="D20" s="20"/>
     </row>
-    <row r="21" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
         <v>34</v>
       </c>
@@ -10110,7 +10127,7 @@
       </c>
       <c r="D21" s="20"/>
     </row>
-    <row r="22" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
         <v>34</v>
       </c>
@@ -10122,7 +10139,7 @@
       </c>
       <c r="D22" s="20"/>
     </row>
-    <row r="23" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
         <v>37</v>
       </c>
@@ -10134,7 +10151,7 @@
       </c>
       <c r="D23" s="23"/>
     </row>
-    <row r="24" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
         <v>37</v>
       </c>
@@ -10146,7 +10163,7 @@
       </c>
       <c r="D24" s="23"/>
     </row>
-    <row r="25" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
         <v>37</v>
       </c>
@@ -10158,7 +10175,7 @@
       </c>
       <c r="D25" s="23"/>
     </row>
-    <row r="26" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
         <v>37</v>
       </c>
@@ -10170,7 +10187,7 @@
       </c>
       <c r="D26" s="23"/>
     </row>
-    <row r="27" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
         <v>40</v>
       </c>
@@ -10182,7 +10199,7 @@
       </c>
       <c r="D27" s="26"/>
     </row>
-    <row r="28" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
         <v>40</v>
       </c>
@@ -10194,7 +10211,7 @@
       </c>
       <c r="D28" s="26"/>
     </row>
-    <row r="29" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
         <v>40</v>
       </c>
@@ -10206,7 +10223,7 @@
       </c>
       <c r="D29" s="26"/>
     </row>
-    <row r="30" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
         <v>40</v>
       </c>
@@ -10218,7 +10235,7 @@
       </c>
       <c r="D30" s="26"/>
     </row>
-    <row r="31" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
         <v>43</v>
       </c>
@@ -10230,7 +10247,7 @@
       </c>
       <c r="D31" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
         <v>43</v>
       </c>
@@ -10242,7 +10259,7 @@
       </c>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
         <v>43</v>
       </c>
@@ -10254,7 +10271,7 @@
       </c>
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>43</v>
       </c>
@@ -10266,7 +10283,7 @@
       </c>
       <c r="D34" s="8"/>
     </row>
-    <row r="35" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
         <v>46</v>
       </c>
@@ -10278,7 +10295,7 @@
       </c>
       <c r="D35" s="11"/>
     </row>
-    <row r="36" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="30" t="s">
         <v>46</v>
       </c>
@@ -10290,7 +10307,7 @@
       </c>
       <c r="D36" s="11"/>
     </row>
-    <row r="37" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="30" t="s">
         <v>46</v>
       </c>
@@ -10302,7 +10319,7 @@
       </c>
       <c r="D37" s="11"/>
     </row>
-    <row r="38" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="30" t="s">
         <v>46</v>
       </c>
@@ -10314,7 +10331,7 @@
       </c>
       <c r="D38" s="11"/>
     </row>
-    <row r="39" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="31" t="s">
         <v>49</v>
       </c>
@@ -10326,7 +10343,7 @@
       </c>
       <c r="D39" s="14"/>
     </row>
-    <row r="40" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="31" t="s">
         <v>49</v>
       </c>
@@ -10338,7 +10355,7 @@
       </c>
       <c r="D40" s="14"/>
     </row>
-    <row r="41" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="31" t="s">
         <v>49</v>
       </c>
@@ -10350,7 +10367,7 @@
       </c>
       <c r="D41" s="14"/>
     </row>
-    <row r="42" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="31" t="s">
         <v>49</v>
       </c>
@@ -10362,7 +10379,7 @@
       </c>
       <c r="D42" s="14"/>
     </row>
-    <row r="43" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="32" t="s">
         <v>52</v>
       </c>
@@ -10374,7 +10391,7 @@
       </c>
       <c r="D43" s="17"/>
     </row>
-    <row r="44" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="32" t="s">
         <v>52</v>
       </c>
@@ -10386,7 +10403,7 @@
       </c>
       <c r="D44" s="17"/>
     </row>
-    <row r="45" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="32" t="s">
         <v>52</v>
       </c>
@@ -10398,7 +10415,7 @@
       </c>
       <c r="D45" s="17"/>
     </row>
-    <row r="46" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="32" t="s">
         <v>52</v>
       </c>
@@ -10410,7 +10427,7 @@
       </c>
       <c r="D46" s="17"/>
     </row>
-    <row r="47" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
         <v>55</v>
       </c>
@@ -10422,7 +10439,7 @@
       </c>
       <c r="D47" s="20"/>
     </row>
-    <row r="48" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="33" t="s">
         <v>55</v>
       </c>
@@ -10434,7 +10451,7 @@
       </c>
       <c r="D48" s="20"/>
     </row>
-    <row r="49" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="33" t="s">
         <v>55</v>
       </c>
@@ -10446,7 +10463,7 @@
       </c>
       <c r="D49" s="20"/>
     </row>
-    <row r="50" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
         <v>55</v>
       </c>
@@ -10469,7 +10486,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I74"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -10479,20 +10496,20 @@
     <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="215" t="s">
+    <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="216" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="216"/>
-      <c r="C1" s="216"/>
-      <c r="D1" s="216"/>
-      <c r="E1" s="216"/>
-      <c r="F1" s="216"/>
-      <c r="G1" s="216"/>
-      <c r="H1" s="216"/>
-      <c r="I1" s="216"/>
-    </row>
-    <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+    </row>
+    <row r="2" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
         <v>127</v>
       </c>
@@ -10521,7 +10538,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="56">
         <v>1</v>
       </c>
@@ -10550,7 +10567,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="56">
         <v>2</v>
       </c>
@@ -10579,7 +10596,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="59">
         <v>3</v>
       </c>
@@ -10608,7 +10625,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="62">
         <v>4</v>
       </c>
@@ -10637,7 +10654,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="59">
         <v>5</v>
       </c>
@@ -10666,7 +10683,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65">
         <v>6</v>
       </c>
@@ -10695,7 +10712,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="65">
         <v>7</v>
       </c>
@@ -10724,7 +10741,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
         <v>8</v>
       </c>
@@ -10753,7 +10770,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="68">
         <v>9</v>
       </c>
@@ -10782,7 +10799,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="71">
         <v>10</v>
       </c>
@@ -10811,7 +10828,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="68">
         <v>11</v>
       </c>
@@ -10840,7 +10857,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="71">
         <v>12</v>
       </c>
@@ -10869,7 +10886,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="56">
         <v>13</v>
       </c>
@@ -10898,7 +10915,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="75">
         <v>14</v>
       </c>
@@ -10927,7 +10944,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="56">
         <v>15</v>
       </c>
@@ -10956,7 +10973,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="75">
         <v>16</v>
       </c>
@@ -10985,7 +11002,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="59">
         <v>17</v>
       </c>
@@ -11014,7 +11031,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="59">
         <v>18</v>
       </c>
@@ -11043,7 +11060,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="65">
         <v>19</v>
       </c>
@@ -11072,7 +11089,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65">
         <v>20</v>
       </c>
@@ -11101,7 +11118,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="62">
         <v>21</v>
       </c>
@@ -11130,7 +11147,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="68">
         <v>22</v>
       </c>
@@ -11159,7 +11176,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="68">
         <v>23</v>
       </c>
@@ -11188,7 +11205,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="62">
         <v>24</v>
       </c>
@@ -11217,7 +11234,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="56">
         <v>25</v>
       </c>
@@ -11246,7 +11263,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="59">
         <v>26</v>
       </c>
@@ -11275,7 +11292,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="59">
         <v>27</v>
       </c>
@@ -11304,7 +11321,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56">
         <v>28</v>
       </c>
@@ -11333,7 +11350,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="62">
         <v>29</v>
       </c>
@@ -11362,7 +11379,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="65">
         <v>30</v>
       </c>
@@ -11391,7 +11408,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="65">
         <v>31</v>
       </c>
@@ -11420,7 +11437,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="62">
         <v>32</v>
       </c>
@@ -11449,7 +11466,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="71">
         <v>33</v>
       </c>
@@ -11478,7 +11495,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="68">
         <v>34</v>
       </c>
@@ -11507,7 +11524,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="68">
         <v>35</v>
       </c>
@@ -11536,7 +11553,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="71">
         <v>36</v>
       </c>
@@ -11565,7 +11582,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="56">
         <v>37</v>
       </c>
@@ -11594,7 +11611,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="75">
         <v>38</v>
       </c>
@@ -11623,7 +11640,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="56">
         <v>39</v>
       </c>
@@ -11652,7 +11669,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="75">
         <v>40</v>
       </c>
@@ -11681,7 +11698,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="65">
         <v>41</v>
       </c>
@@ -11710,7 +11727,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="59">
         <v>42</v>
       </c>
@@ -11739,7 +11756,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="59">
         <v>43</v>
       </c>
@@ -11768,7 +11785,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="65">
         <v>44</v>
       </c>
@@ -11797,7 +11814,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="62">
         <v>45</v>
       </c>
@@ -11826,7 +11843,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="68">
         <v>46</v>
       </c>
@@ -11855,7 +11872,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="68">
         <v>47</v>
       </c>
@@ -11884,7 +11901,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="62">
         <v>48</v>
       </c>
@@ -11913,7 +11930,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="59">
         <v>49</v>
       </c>
@@ -11942,7 +11959,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="59">
         <v>50</v>
       </c>
@@ -11971,7 +11988,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="65">
         <v>51</v>
       </c>
@@ -12000,7 +12017,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="65">
         <v>52</v>
       </c>
@@ -12029,7 +12046,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="56">
         <v>53</v>
       </c>
@@ -12058,7 +12075,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="56">
         <v>54</v>
       </c>
@@ -12087,7 +12104,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="68">
         <v>55</v>
       </c>
@@ -12116,7 +12133,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="68">
         <v>56</v>
       </c>
@@ -12145,7 +12162,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="71">
         <v>57</v>
       </c>
@@ -12174,7 +12191,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="71">
         <v>58</v>
       </c>
@@ -12203,7 +12220,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="62">
         <v>59</v>
       </c>
@@ -12232,7 +12249,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="62">
         <v>60</v>
       </c>
@@ -12261,7 +12278,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="59">
         <v>61</v>
       </c>
@@ -12290,7 +12307,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>62</v>
       </c>
@@ -12319,7 +12336,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="56">
         <v>63</v>
       </c>
@@ -12348,7 +12365,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="56">
         <v>64</v>
       </c>
@@ -12377,7 +12394,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="75">
         <v>65</v>
       </c>
@@ -12406,7 +12423,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="75">
         <v>66</v>
       </c>
@@ -12435,7 +12452,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="68">
         <v>67</v>
       </c>
@@ -12464,7 +12481,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="68">
         <v>68</v>
       </c>
@@ -12493,7 +12510,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="62">
         <v>69</v>
       </c>
@@ -12522,7 +12539,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="62">
         <v>70</v>
       </c>
@@ -12551,7 +12568,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="65">
         <v>71</v>
       </c>
@@ -12580,7 +12597,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="65">
         <v>72</v>
       </c>
@@ -12620,12 +12637,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K496"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="11" width="48.26953125" customWidth="1"/>
+    <col min="11" max="11" width="48.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>357</v>
       </c>
@@ -12660,7 +12677,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -12695,7 +12712,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -12730,7 +12747,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -12765,7 +12782,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -12800,7 +12817,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -12835,7 +12852,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -12870,7 +12887,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -12905,7 +12922,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -12940,7 +12957,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -12975,7 +12992,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -13010,7 +13027,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -13045,7 +13062,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -13080,7 +13097,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -13115,7 +13132,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -13150,7 +13167,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -13185,7 +13202,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -13220,7 +13237,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -13255,7 +13272,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -13290,7 +13307,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -13325,7 +13342,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -13360,7 +13377,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -13395,7 +13412,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -13430,7 +13447,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -13465,7 +13482,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -13500,7 +13517,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -13535,7 +13552,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -13570,7 +13587,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -13605,7 +13622,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -13640,7 +13657,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -13675,7 +13692,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -13710,7 +13727,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -13745,7 +13762,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -13780,7 +13797,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -13815,7 +13832,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -13850,7 +13867,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -13885,7 +13902,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -13920,7 +13937,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -13955,7 +13972,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -13990,7 +14007,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -14025,7 +14042,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -14060,7 +14077,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -14095,7 +14112,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -14130,7 +14147,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -14165,7 +14182,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -14200,7 +14217,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -14235,7 +14252,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -14270,7 +14287,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -14305,7 +14322,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -14340,7 +14357,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -14375,7 +14392,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -14410,7 +14427,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -14445,7 +14462,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -14480,7 +14497,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -14515,7 +14532,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -14550,7 +14567,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -14585,7 +14602,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -14620,7 +14637,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -14655,7 +14672,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -14690,7 +14707,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -14725,7 +14742,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -14760,7 +14777,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -14795,7 +14812,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -14830,7 +14847,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -14865,7 +14882,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -14900,7 +14917,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -14935,7 +14952,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -14970,7 +14987,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -15005,7 +15022,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -15040,7 +15057,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -15075,7 +15092,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -15110,7 +15127,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -15145,7 +15162,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -15180,7 +15197,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -15215,7 +15232,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -15250,7 +15267,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -15285,7 +15302,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -15320,7 +15337,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -15355,7 +15372,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -15390,7 +15407,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -15425,7 +15442,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -15460,7 +15477,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -15495,7 +15512,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -15530,7 +15547,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -15565,7 +15582,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -15600,7 +15617,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -15635,7 +15652,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -15670,7 +15687,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -15705,7 +15722,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -15740,7 +15757,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -15775,7 +15792,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -15810,7 +15827,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -15845,7 +15862,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -15880,7 +15897,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -15915,7 +15932,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -15950,7 +15967,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -15985,7 +16002,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -16020,7 +16037,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -16055,7 +16072,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -16090,7 +16107,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -16125,7 +16142,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -16160,7 +16177,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -16195,7 +16212,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -16230,7 +16247,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -16265,7 +16282,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -16300,7 +16317,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -16335,7 +16352,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -16370,7 +16387,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -16405,7 +16422,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -16440,7 +16457,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -16475,7 +16492,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -16510,7 +16527,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -16545,7 +16562,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -16580,7 +16597,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -16615,7 +16632,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -16650,7 +16667,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -16685,7 +16702,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -16720,7 +16737,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -16755,7 +16772,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -16790,7 +16807,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -16825,7 +16842,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -16860,7 +16877,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -16895,7 +16912,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -16930,7 +16947,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -16965,7 +16982,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -17000,7 +17017,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -17035,7 +17052,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -17070,7 +17087,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -17105,7 +17122,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -17140,7 +17157,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -17175,7 +17192,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -17210,7 +17227,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -17245,7 +17262,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -17280,7 +17297,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -17315,7 +17332,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -17350,7 +17367,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -17385,7 +17402,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -17420,7 +17437,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -17455,7 +17472,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -17490,7 +17507,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -17525,7 +17542,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -17560,7 +17577,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -17595,7 +17612,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -17630,7 +17647,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -17665,7 +17682,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -17700,7 +17717,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -17735,7 +17752,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -17770,7 +17787,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -17805,7 +17822,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -17840,7 +17857,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -17875,7 +17892,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -17910,7 +17927,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -17945,7 +17962,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -17980,7 +17997,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -18015,7 +18032,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -18050,7 +18067,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -18085,7 +18102,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -18120,7 +18137,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -18155,7 +18172,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -18190,7 +18207,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -18225,7 +18242,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -18260,7 +18277,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -18295,7 +18312,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -18330,7 +18347,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -18365,7 +18382,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -18400,7 +18417,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -18435,7 +18452,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -18470,7 +18487,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -18505,7 +18522,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -18540,7 +18557,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -18575,7 +18592,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -18610,7 +18627,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -18645,7 +18662,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -18680,7 +18697,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -18715,7 +18732,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -18750,7 +18767,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -18785,7 +18802,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -18820,7 +18837,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -18855,7 +18872,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -18890,7 +18907,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -18925,7 +18942,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -18960,7 +18977,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -18995,7 +19012,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -19030,7 +19047,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -19065,7 +19082,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -19100,7 +19117,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -19135,7 +19152,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -19170,7 +19187,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -19205,7 +19222,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -19240,7 +19257,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -19275,7 +19292,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -19310,7 +19327,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -19345,7 +19362,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -19380,7 +19397,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -19415,7 +19432,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -19450,7 +19467,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -19485,7 +19502,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -19520,7 +19537,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -19555,7 +19572,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -19590,7 +19607,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -19625,7 +19642,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -19660,7 +19677,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -19695,7 +19712,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -19730,7 +19747,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -19765,7 +19782,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -19800,7 +19817,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -19835,7 +19852,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -19870,7 +19887,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -19905,7 +19922,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -19940,7 +19957,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -19975,7 +19992,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -20010,7 +20027,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -20045,7 +20062,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -20080,7 +20097,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -20115,7 +20132,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -20150,7 +20167,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -20185,7 +20202,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -20220,7 +20237,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -20255,7 +20272,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -20290,7 +20307,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -20325,7 +20342,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -20360,7 +20377,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -20395,7 +20412,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -20430,7 +20447,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -20465,7 +20482,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -20500,7 +20517,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -20535,7 +20552,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -20570,7 +20587,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -20605,7 +20622,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -20640,7 +20657,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -20675,7 +20692,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -20710,7 +20727,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -20745,7 +20762,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -20780,7 +20797,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -20815,7 +20832,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -20850,7 +20867,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -20885,7 +20902,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -20920,7 +20937,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -20955,7 +20972,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -20990,7 +21007,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -21025,7 +21042,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -21060,7 +21077,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -21095,7 +21112,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -21130,7 +21147,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -21165,7 +21182,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -21200,7 +21217,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -21235,7 +21252,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -21270,7 +21287,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -21305,7 +21322,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -21340,7 +21357,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -21375,7 +21392,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -21410,7 +21427,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -21445,7 +21462,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -21480,7 +21497,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -21515,7 +21532,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -21550,7 +21567,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -21585,7 +21602,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -21620,7 +21637,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -21655,7 +21672,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -21690,7 +21707,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -21725,7 +21742,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -21760,7 +21777,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -21795,7 +21812,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -21830,7 +21847,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -21865,7 +21882,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -21900,7 +21917,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -21935,7 +21952,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -21970,7 +21987,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -22005,7 +22022,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -22040,7 +22057,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -22075,7 +22092,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -22110,7 +22127,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -22145,7 +22162,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -22180,7 +22197,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -22215,7 +22232,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -22250,7 +22267,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -22285,7 +22302,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -22320,7 +22337,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -22355,7 +22372,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -22390,7 +22407,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -22425,7 +22442,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -22460,7 +22477,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -22495,7 +22512,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -22530,7 +22547,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -22565,7 +22582,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -22600,7 +22617,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -22635,7 +22652,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -22670,7 +22687,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -22705,7 +22722,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
@@ -22740,7 +22757,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
@@ -22775,7 +22792,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
@@ -22810,7 +22827,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
@@ -22845,7 +22862,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>292</v>
       </c>
@@ -22880,7 +22897,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
@@ -22915,7 +22932,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
@@ -22950,7 +22967,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
@@ -22985,7 +23002,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
@@ -23020,7 +23037,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>297</v>
       </c>
@@ -23055,7 +23072,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
@@ -23090,7 +23107,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
@@ -23125,7 +23142,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>300</v>
       </c>
@@ -23160,7 +23177,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>301</v>
       </c>
@@ -23195,7 +23212,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>302</v>
       </c>
@@ -23230,7 +23247,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>303</v>
       </c>
@@ -23265,7 +23282,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>304</v>
       </c>
@@ -23300,7 +23317,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>305</v>
       </c>
@@ -23335,7 +23352,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>306</v>
       </c>
@@ -23370,7 +23387,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>307</v>
       </c>
@@ -23405,7 +23422,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>308</v>
       </c>
@@ -23440,7 +23457,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>309</v>
       </c>
@@ -23475,7 +23492,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>310</v>
       </c>
@@ -23510,7 +23527,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>311</v>
       </c>
@@ -23545,7 +23562,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>312</v>
       </c>
@@ -23580,7 +23597,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>313</v>
       </c>
@@ -23615,7 +23632,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
@@ -23650,7 +23667,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>315</v>
       </c>
@@ -23685,7 +23702,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>316</v>
       </c>
@@ -23720,7 +23737,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>317</v>
       </c>
@@ -23755,7 +23772,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>318</v>
       </c>
@@ -23790,7 +23807,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>319</v>
       </c>
@@ -23825,7 +23842,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
@@ -23860,7 +23877,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>321</v>
       </c>
@@ -23895,7 +23912,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>322</v>
       </c>
@@ -23930,7 +23947,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>323</v>
       </c>
@@ -23965,7 +23982,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>324</v>
       </c>
@@ -24000,7 +24017,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>325</v>
       </c>
@@ -24035,7 +24052,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>326</v>
       </c>
@@ -24070,7 +24087,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>327</v>
       </c>
@@ -24105,7 +24122,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>328</v>
       </c>
@@ -24140,7 +24157,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>329</v>
       </c>
@@ -24175,7 +24192,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>330</v>
       </c>
@@ -24210,7 +24227,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>331</v>
       </c>
@@ -24245,7 +24262,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>332</v>
       </c>
@@ -24280,7 +24297,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>333</v>
       </c>
@@ -24315,7 +24332,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>334</v>
       </c>
@@ -24350,7 +24367,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>335</v>
       </c>
@@ -24385,7 +24402,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>336</v>
       </c>
@@ -24420,7 +24437,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>337</v>
       </c>
@@ -24455,7 +24472,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>338</v>
       </c>
@@ -24490,7 +24507,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>339</v>
       </c>
@@ -24525,7 +24542,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>340</v>
       </c>
@@ -24560,7 +24577,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>341</v>
       </c>
@@ -24595,7 +24612,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>342</v>
       </c>
@@ -24630,7 +24647,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>343</v>
       </c>
@@ -24665,7 +24682,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>344</v>
       </c>
@@ -24700,7 +24717,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>345</v>
       </c>
@@ -24735,7 +24752,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>346</v>
       </c>
@@ -24770,7 +24787,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>347</v>
       </c>
@@ -24805,7 +24822,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>348</v>
       </c>
@@ -24840,7 +24857,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>349</v>
       </c>
@@ -24875,7 +24892,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>350</v>
       </c>
@@ -24910,7 +24927,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>351</v>
       </c>
@@ -24945,7 +24962,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>352</v>
       </c>
@@ -24980,7 +24997,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>353</v>
       </c>
@@ -25015,7 +25032,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>354</v>
       </c>
@@ -25050,7 +25067,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>355</v>
       </c>
@@ -25085,7 +25102,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>356</v>
       </c>
@@ -25120,7 +25137,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>357</v>
       </c>
@@ -25155,7 +25172,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>358</v>
       </c>
@@ -25190,7 +25207,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>359</v>
       </c>
@@ -25225,7 +25242,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>360</v>
       </c>
@@ -25260,7 +25277,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>361</v>
       </c>
@@ -25295,7 +25312,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>362</v>
       </c>
@@ -25330,7 +25347,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>363</v>
       </c>
@@ -25365,7 +25382,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>364</v>
       </c>
@@ -25400,7 +25417,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>365</v>
       </c>
@@ -25435,7 +25452,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>366</v>
       </c>
@@ -25470,7 +25487,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>367</v>
       </c>
@@ -25505,7 +25522,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>368</v>
       </c>
@@ -25540,7 +25557,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>369</v>
       </c>
@@ -25575,7 +25592,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>370</v>
       </c>
@@ -25610,7 +25627,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>371</v>
       </c>
@@ -25645,7 +25662,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>372</v>
       </c>
@@ -25680,7 +25697,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>373</v>
       </c>
@@ -25715,7 +25732,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>374</v>
       </c>
@@ -25750,7 +25767,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>375</v>
       </c>
@@ -25785,7 +25802,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>376</v>
       </c>
@@ -25820,7 +25837,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>377</v>
       </c>
@@ -25855,7 +25872,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>378</v>
       </c>
@@ -25890,7 +25907,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>379</v>
       </c>
@@ -25925,7 +25942,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>380</v>
       </c>
@@ -25960,7 +25977,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>381</v>
       </c>
@@ -25995,7 +26012,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>382</v>
       </c>
@@ -26030,7 +26047,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>383</v>
       </c>
@@ -26065,7 +26082,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>384</v>
       </c>
@@ -26100,7 +26117,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>385</v>
       </c>
@@ -26135,7 +26152,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>386</v>
       </c>
@@ -26170,7 +26187,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>387</v>
       </c>
@@ -26205,7 +26222,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>388</v>
       </c>
@@ -26240,7 +26257,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>389</v>
       </c>
@@ -26275,7 +26292,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>390</v>
       </c>
@@ -26310,7 +26327,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>391</v>
       </c>
@@ -26345,7 +26362,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>392</v>
       </c>
@@ -26380,7 +26397,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>393</v>
       </c>
@@ -26415,7 +26432,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>394</v>
       </c>
@@ -26450,7 +26467,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>395</v>
       </c>
@@ -26485,7 +26502,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>396</v>
       </c>
@@ -26520,7 +26537,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>397</v>
       </c>
@@ -26555,7 +26572,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>398</v>
       </c>
@@ -26590,7 +26607,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>399</v>
       </c>
@@ -26625,7 +26642,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>400</v>
       </c>
@@ -26660,7 +26677,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>401</v>
       </c>
@@ -26695,7 +26712,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>402</v>
       </c>
@@ -26730,7 +26747,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>403</v>
       </c>
@@ -26765,7 +26782,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>404</v>
       </c>
@@ -26800,7 +26817,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>405</v>
       </c>
@@ -26835,7 +26852,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>406</v>
       </c>
@@ -26870,7 +26887,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>407</v>
       </c>
@@ -26905,7 +26922,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>408</v>
       </c>
@@ -26940,7 +26957,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>409</v>
       </c>
@@ -26975,7 +26992,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>410</v>
       </c>
@@ -27010,7 +27027,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>411</v>
       </c>
@@ -27045,7 +27062,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>412</v>
       </c>
@@ -27080,7 +27097,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>413</v>
       </c>
@@ -27115,7 +27132,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>414</v>
       </c>
@@ -27150,7 +27167,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>415</v>
       </c>
@@ -27185,7 +27202,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>416</v>
       </c>
@@ -27220,7 +27237,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>417</v>
       </c>
@@ -27255,7 +27272,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>418</v>
       </c>
@@ -27290,7 +27307,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>419</v>
       </c>
@@ -27325,7 +27342,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>420</v>
       </c>
@@ -27360,7 +27377,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>421</v>
       </c>
@@ -27395,7 +27412,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>422</v>
       </c>
@@ -27430,7 +27447,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>423</v>
       </c>
@@ -27465,7 +27482,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>424</v>
       </c>
@@ -27500,7 +27517,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>425</v>
       </c>
@@ -27535,7 +27552,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>426</v>
       </c>
@@ -27570,7 +27587,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>427</v>
       </c>
@@ -27605,7 +27622,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>428</v>
       </c>
@@ -27640,7 +27657,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>429</v>
       </c>
@@ -27675,7 +27692,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>430</v>
       </c>
@@ -27710,7 +27727,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>431</v>
       </c>
@@ -27745,7 +27762,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>432</v>
       </c>
@@ -27780,7 +27797,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>433</v>
       </c>
@@ -27815,7 +27832,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>434</v>
       </c>
@@ -27850,7 +27867,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>435</v>
       </c>
@@ -27885,7 +27902,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>436</v>
       </c>
@@ -27920,7 +27937,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>437</v>
       </c>
@@ -27955,7 +27972,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>438</v>
       </c>
@@ -27990,7 +28007,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>439</v>
       </c>
@@ -28025,7 +28042,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>440</v>
       </c>
@@ -28060,7 +28077,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>441</v>
       </c>
@@ -28095,7 +28112,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>442</v>
       </c>
@@ -28130,7 +28147,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>443</v>
       </c>
@@ -28165,7 +28182,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>444</v>
       </c>
@@ -28200,7 +28217,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>445</v>
       </c>
@@ -28235,7 +28252,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>446</v>
       </c>
@@ -28270,7 +28287,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>447</v>
       </c>
@@ -28305,7 +28322,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>448</v>
       </c>
@@ -28340,7 +28357,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>449</v>
       </c>
@@ -28375,7 +28392,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>450</v>
       </c>
@@ -28410,7 +28427,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>451</v>
       </c>
@@ -28445,7 +28462,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>452</v>
       </c>
@@ -28480,7 +28497,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>453</v>
       </c>
@@ -28515,7 +28532,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>454</v>
       </c>
@@ -28550,7 +28567,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>455</v>
       </c>
@@ -28585,7 +28602,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>456</v>
       </c>
@@ -28620,7 +28637,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>457</v>
       </c>
@@ -28655,7 +28672,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>458</v>
       </c>
@@ -28690,7 +28707,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>459</v>
       </c>
@@ -28725,7 +28742,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>460</v>
       </c>
@@ -28760,7 +28777,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>461</v>
       </c>
@@ -28795,7 +28812,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>462</v>
       </c>
@@ -28830,7 +28847,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>463</v>
       </c>
@@ -28865,7 +28882,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>464</v>
       </c>
@@ -28900,7 +28917,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>465</v>
       </c>
@@ -28935,7 +28952,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>466</v>
       </c>
@@ -28970,7 +28987,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>467</v>
       </c>
@@ -29005,7 +29022,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>468</v>
       </c>
@@ -29040,7 +29057,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>469</v>
       </c>
@@ -29075,7 +29092,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>470</v>
       </c>
@@ -29110,7 +29127,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>471</v>
       </c>
@@ -29145,7 +29162,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>472</v>
       </c>
@@ -29180,7 +29197,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>473</v>
       </c>
@@ -29215,7 +29232,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>474</v>
       </c>
@@ -29250,7 +29267,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>475</v>
       </c>
@@ -29285,7 +29302,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>476</v>
       </c>
@@ -29320,7 +29337,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>477</v>
       </c>
@@ -29355,7 +29372,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>478</v>
       </c>
@@ -29390,7 +29407,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>479</v>
       </c>
@@ -29425,7 +29442,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>480</v>
       </c>
@@ -29460,7 +29477,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>481</v>
       </c>
@@ -29495,7 +29512,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>482</v>
       </c>
@@ -29530,7 +29547,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>483</v>
       </c>
@@ -29565,7 +29582,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>484</v>
       </c>
@@ -29600,7 +29617,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>485</v>
       </c>
@@ -29635,7 +29652,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>486</v>
       </c>
@@ -29670,7 +29687,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>487</v>
       </c>
@@ -29705,7 +29722,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>488</v>
       </c>
@@ -29740,7 +29757,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>489</v>
       </c>
@@ -29775,7 +29792,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>490</v>
       </c>
@@ -29810,7 +29827,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>491</v>
       </c>
@@ -29845,7 +29862,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>492</v>
       </c>
@@ -29880,7 +29897,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>493</v>
       </c>
@@ -29915,7 +29932,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>494</v>
       </c>
@@ -29950,7 +29967,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>495</v>
       </c>
@@ -29993,15 +30010,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:CA49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="13.1796875" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="19" max="56" width="13" hidden="1" customWidth="1"/>
     <col min="58" max="67" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>238</v>
       </c>
@@ -30181,19 +30198,19 @@
       <c r="BO1" t="s">
         <v>292</v>
       </c>
-      <c r="BT1" s="217" t="s">
+      <c r="BT1" s="218" t="s">
         <v>316</v>
       </c>
-      <c r="BU1" s="216"/>
-      <c r="BV1" s="216"/>
-      <c r="BX1" s="218" t="s">
+      <c r="BU1" s="217"/>
+      <c r="BV1" s="217"/>
+      <c r="BX1" s="219" t="s">
         <v>317</v>
       </c>
-      <c r="BY1" s="216"/>
-      <c r="BZ1" s="216"/>
-      <c r="CA1" s="216"/>
-    </row>
-    <row r="2" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="BY1" s="217"/>
+      <c r="BZ1" s="217"/>
+      <c r="CA1" s="217"/>
+    </row>
+    <row r="2" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -30452,7 +30469,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -30708,7 +30725,7 @@
       </c>
       <c r="CA3" s="143"/>
     </row>
-    <row r="4" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -30855,7 +30872,7 @@
       </c>
       <c r="CA4" s="143"/>
     </row>
-    <row r="5" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -31002,7 +31019,7 @@
       </c>
       <c r="CA5" s="143"/>
     </row>
-    <row r="6" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -31146,7 +31163,7 @@
       </c>
       <c r="CA6" s="143"/>
     </row>
-    <row r="7" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -31266,7 +31283,7 @@
       </c>
       <c r="CA7" s="143"/>
     </row>
-    <row r="8" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -31386,7 +31403,7 @@
       </c>
       <c r="CA8" s="143"/>
     </row>
-    <row r="9" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -31506,7 +31523,7 @@
       </c>
       <c r="CA9" s="143"/>
     </row>
-    <row r="10" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -31618,7 +31635,7 @@
       </c>
       <c r="CA10" s="143"/>
     </row>
-    <row r="11" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -31730,7 +31747,7 @@
       </c>
       <c r="CA11" s="143"/>
     </row>
-    <row r="12" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -31842,7 +31859,7 @@
       </c>
       <c r="CA12" s="143"/>
     </row>
-    <row r="13" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -31954,7 +31971,7 @@
       </c>
       <c r="CA13" s="143"/>
     </row>
-    <row r="14" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -32029,7 +32046,7 @@
       </c>
       <c r="CA14" s="143"/>
     </row>
-    <row r="15" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -32104,7 +32121,7 @@
       </c>
       <c r="CA15" s="143"/>
     </row>
-    <row r="16" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>59</v>
       </c>
@@ -32179,7 +32196,7 @@
       </c>
       <c r="CA16" s="143"/>
     </row>
-    <row r="17" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -32254,7 +32271,7 @@
       </c>
       <c r="CA17" s="143"/>
     </row>
-    <row r="18" spans="1:79" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -32329,7 +32346,7 @@
       </c>
       <c r="CA18" s="143"/>
     </row>
-    <row r="19" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -32392,7 +32409,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="20" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -32455,7 +32472,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="21" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>69</v>
       </c>
@@ -32517,14 +32534,14 @@
       <c r="BV21" s="139" t="s">
         <v>340</v>
       </c>
-      <c r="BX21" s="217" t="s">
+      <c r="BX21" s="218" t="s">
         <v>341</v>
       </c>
-      <c r="BY21" s="216"/>
-      <c r="BZ21" s="216"/>
-      <c r="CA21" s="216"/>
-    </row>
-    <row r="22" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="BY21" s="217"/>
+      <c r="BZ21" s="217"/>
+      <c r="CA21" s="217"/>
+    </row>
+    <row r="22" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>71</v>
       </c>
@@ -32595,7 +32612,7 @@
       <c r="BZ22" s="145"/>
       <c r="CA22" s="145"/>
     </row>
-    <row r="23" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -32666,7 +32683,7 @@
       <c r="BZ23" s="145"/>
       <c r="CA23" s="145"/>
     </row>
-    <row r="24" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -32737,7 +32754,7 @@
       <c r="BZ24" s="145"/>
       <c r="CA24" s="145"/>
     </row>
-    <row r="25" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>77</v>
       </c>
@@ -32800,7 +32817,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="26" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -32863,7 +32880,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="27" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>81</v>
       </c>
@@ -32916,7 +32933,7 @@
       <c r="AY27" s="86"/>
       <c r="AZ27" s="86"/>
     </row>
-    <row r="28" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>83</v>
       </c>
@@ -32969,7 +32986,7 @@
       <c r="AY28" s="86"/>
       <c r="AZ28" s="86"/>
     </row>
-    <row r="29" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -33022,7 +33039,7 @@
       <c r="AY29" s="86"/>
       <c r="AZ29" s="86"/>
     </row>
-    <row r="30" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -33075,97 +33092,97 @@
       <c r="AY30" s="86"/>
       <c r="AZ30" s="86"/>
     </row>
-    <row r="31" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>124</v>
       </c>
